--- a/results/Int All Data 0.1/Rando_4_permute.xlsx
+++ b/results/Int All Data 0.1/Rando_4_permute.xlsx
@@ -440,977 +440,977 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9493567572588488</v>
+        <v>0.9340741074648395</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9533556808619917</v>
+        <v>0.9361927515326361</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9533556808619917</v>
+        <v>0.9362309991366969</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9577077118097674</v>
+        <v>0.9363614507862614</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9591583887923593</v>
+        <v>0.9363614507862614</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9583217224535292</v>
+        <v>0.9348185697581659</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.954100143155318</v>
+        <v>0.9348185697581659</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9492645532133451</v>
+        <v>0.941028341474609</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9487809942191479</v>
+        <v>0.941028341474609</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9492645532133451</v>
+        <v>0.9437452873487854</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9457874362084604</v>
+        <v>0.9359543870001859</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9450812215191948</v>
+        <v>0.9359543870001859</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9449507698696303</v>
+        <v>0.9340201510233966</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.945917887858025</v>
+        <v>0.9262449595121791</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9430165338928411</v>
+        <v>0.9268589701559409</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9427016741522691</v>
+        <v>0.9151231026456415</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9412892447737381</v>
+        <v>0.9185462632090833</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9412892447737381</v>
+        <v>0.9188993705537161</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9320633762799287</v>
+        <v>0.9185462632090833</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9352795899856845</v>
+        <v>0.9170955862264913</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9340898163022217</v>
+        <v>0.9153300495033275</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9365998153187118</v>
+        <v>0.9174486935711241</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9355404932848135</v>
+        <v>0.9165129932574938</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9344811712509151</v>
+        <v>0.9049075773967588</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9344811712509151</v>
+        <v>0.9049075773967588</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9284783463921581</v>
+        <v>0.9005555464489832</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9237732080997498</v>
+        <v>0.9117538985236424</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9226756384617907</v>
+        <v>0.9125523172584118</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9249629817832126</v>
+        <v>0.9067496093280443</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9250777245953949</v>
+        <v>0.8903086035253363</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9250777245953949</v>
+        <v>0.8896945928815745</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9255612835895923</v>
+        <v>0.8875377012097171</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9298525281666284</v>
+        <v>0.8859565725775607</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9296298724715601</v>
+        <v>0.8865705832213224</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9309883454086483</v>
+        <v>0.882756067709187</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9334983444251386</v>
+        <v>0.892427247593133</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9334983444251386</v>
+        <v>0.895758204111071</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.928516593996219</v>
+        <v>0.8897328404856353</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.928516593996219</v>
+        <v>0.8885430668021724</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9280330350020216</v>
+        <v>0.8880595078079752</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9260830901878503</v>
+        <v>0.8864783791758188</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.924187101815122</v>
+        <v>0.8864783791758188</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.9226442207870265</v>
+        <v>0.8875759488137779</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9231660273852845</v>
+        <v>0.882441207968615</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9253454578238206</v>
+        <v>0.8818271973248533</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9158047295894393</v>
+        <v>0.8951441934673092</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.9155820738943711</v>
+        <v>0.8951441934673092</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.9117900971489143</v>
+        <v>0.8951441934673092</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.9131103224819417</v>
+        <v>0.8976541924837994</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.9154673310821886</v>
+        <v>0.8976541924837994</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.9114144510376029</v>
+        <v>0.9067113617239835</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.9118980100318002</v>
+        <v>0.9052606847413915</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.9075616879214066</v>
+        <v>0.9049075773967588</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.9040306144750789</v>
+        <v>0.9033264487646024</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.9149072768798697</v>
+        <v>0.9113762034335421</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.9149072768798697</v>
+        <v>0.9086435487219836</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.9149072768798697</v>
+        <v>0.9090888601121201</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.89938626255341</v>
+        <v>0.9099794828923931</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.9026789714672874</v>
+        <v>0.9099794828923931</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.9032390256696062</v>
+        <v>0.9117586794741501</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.9122961949097903</v>
+        <v>0.9012959107847316</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.9148219027636626</v>
+        <v>0.9033763072484673</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.9102089685167579</v>
+        <v>0.9043816728409227</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.9036529193849785</v>
+        <v>0.8998069861980789</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.9031536515533991</v>
+        <v>0.894341676774962</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8986015036772339</v>
+        <v>0.8853992503469603</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.9073977696182889</v>
+        <v>0.8853992503469603</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.9073977696182889</v>
+        <v>0.8906419040750091</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.9062619523762689</v>
+        <v>0.8954549552503033</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.9063924040258335</v>
+        <v>0.9008888469986559</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.9063924040258335</v>
+        <v>0.8491193489165001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8978187937798467</v>
+        <v>0.8467015539455136</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8934128063906283</v>
+        <v>0.8466093499000098</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8862516255231725</v>
+        <v>0.8459031352107442</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8888155809811057</v>
+        <v>0.8228972013681715</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8946790752822127</v>
+        <v>0.8211316646450076</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8913706575309532</v>
+        <v>0.8206481056508104</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8970203750450776</v>
+        <v>0.8265812652307423</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.892875290954988</v>
+        <v>0.8265812652307423</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8910715066277635</v>
+        <v>0.8336434121233978</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.8905497000295053</v>
+        <v>0.8297592313324372</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.8765961544766089</v>
+        <v>0.8231109781551541</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.8770797134708062</v>
+        <v>0.8211767421783649</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8815239484640855</v>
+        <v>0.8463846452261525</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.8794592608377318</v>
+        <v>0.8542452108535772</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.879418964254882</v>
+        <v>0.8566561758952671</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.8745068791047875</v>
+        <v>0.858106852877859</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.8750040979575779</v>
+        <v>0.8620449901102624</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.8597146182342721</v>
+        <v>0.8402445387885344</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.8600677255789049</v>
+        <v>0.8540628517413588</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.8334719808980537</v>
+        <v>0.8566582248740561</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.828406905331716</v>
+        <v>0.8487839993880384</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.8258969063152258</v>
+        <v>0.8655890404222536</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.8266256597711701</v>
+        <v>0.8750826421444886</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.8245295544700522</v>
+        <v>0.8805861991716661</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.8235624364816576</v>
+        <v>0.8328087947633567</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.8232093291370248</v>
+        <v>0.8365625239047525</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.8227257701428274</v>
+        <v>0.8228835415095783</v>
       </c>
     </row>
     <row r="100">
@@ -1420,117 +1420,117 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.8207915341660383</v>
+        <v>0.825577948617076</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.8108751598203455</v>
+        <v>0.8213789080855436</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.8170220961872603</v>
+        <v>0.8242037668426057</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.8233083631118251</v>
+        <v>0.845037100175939</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.8380152498661333</v>
+        <v>0.8390117365505032</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.8175773694390716</v>
+        <v>0.8433029811275394</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.8044741500835983</v>
+        <v>0.8450213913385569</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.8240685342425336</v>
+        <v>0.8257015703373438</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.8098834540864832</v>
+        <v>0.8215339474805756</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.8182569474040804</v>
+        <v>0.8227237211640385</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.800655536613885</v>
+        <v>0.8227237211640385</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.7887735086166388</v>
+        <v>0.8265136489307063</v>
       </c>
     </row>
     <row r="112">
@@ -1540,447 +1540,447 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.7936473461626725</v>
+        <v>0.8265136489307063</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.7936473461626725</v>
+        <v>0.8258074342414408</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.7930872919603537</v>
+        <v>0.8247098646034816</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.7766353582707712</v>
+        <v>0.8391490181293644</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.7975677255789049</v>
+        <v>0.8395629118447365</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.7894462566523511</v>
+        <v>0.8218399283130621</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.7387067119081183</v>
+        <v>0.8003611666612027</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.7356749062933701</v>
+        <v>0.7511467451288945</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.7356749062933701</v>
+        <v>0.7339387382661815</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.6884411642570676</v>
+        <v>0.7425505961162291</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.688924723251265</v>
+        <v>0.7429037034608618</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.6901144969347277</v>
+        <v>0.7429037034608618</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.6896309379405305</v>
+        <v>0.7429037034608618</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.6976984504256412</v>
+        <v>0.7440934771443246</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.7256997945557268</v>
+        <v>0.7440934771443246</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.7172634658886011</v>
+        <v>0.7924466445923352</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.724073588390213</v>
+        <v>0.7924466445923352</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.6781962703122097</v>
+        <v>0.6937521172780819</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.6712577451398223</v>
+        <v>0.6888311532199018</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.670198423105924</v>
+        <v>0.6966603011725623</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.6489354872198363</v>
+        <v>0.6949487208908414</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.6969225704575506</v>
+        <v>0.6949487208908414</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.6969225704575506</v>
+        <v>0.7055801888338852</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.6915808827547016</v>
+        <v>0.7118370870624747</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.6390669223792196</v>
+        <v>0.7095497437410528</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.6390669223792196</v>
+        <v>0.7078764110633926</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.6405715558032543</v>
+        <v>0.7126218459386509</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.6176106994940388</v>
+        <v>0.7126218459386509</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.6245061961118579</v>
+        <v>0.7126218459386509</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5854349025778884</v>
+        <v>0.5746941557660995</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.581793867269886</v>
+        <v>0.5750206263864757</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.6095390890513501</v>
+        <v>0.5750206263864757</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.6094468850058464</v>
+        <v>0.6204027745904774</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.6129690795440885</v>
+        <v>0.6204027745904774</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.587248931799058</v>
+        <v>0.6204027745904774</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5608690128839786</v>
+        <v>0.6416657104765652</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5108630025461977</v>
+        <v>0.6217182189729972</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5228304046596509</v>
+        <v>0.6217182189729972</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5021343529051787</v>
+        <v>0.5490832868898141</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5021343529051787</v>
+        <v>0.5653890600924499</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5021343529051787</v>
+        <v>0.574077413150619</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4997390967008709</v>
+        <v>0.5845538416986307</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4992555377066736</v>
+        <v>0.5845538416986307</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4995164410058027</v>
+        <v>0.5850148619261493</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5</v>
+        <v>0.5144330065895157</v>
       </c>
     </row>
   </sheetData>
